--- a/root_domains.xlsx
+++ b/root_domains.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Oxford\Master Thesis\Data for DNA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A2B693-C2F2-4AFB-9D55-5B18A0C796FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB8105C-BA4F-4725-AB46-21CA875CD854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7280" yWindow="-13350" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,31 +36,127 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>domain</t>
   </si>
   <si>
-    <t>aerzteblatt.de</t>
-  </si>
-  <si>
-    <t>bfarm.de</t>
-  </si>
-  <si>
-    <t>rki.de</t>
-  </si>
-  <si>
-    <t>pei.de</t>
+    <t>ey.com/de_de</t>
+  </si>
+  <si>
+    <t>kpmg.com/de/de/</t>
+  </si>
+  <si>
+    <t>deloitte.com/de</t>
+  </si>
+  <si>
+    <t>pwc.de</t>
+  </si>
+  <si>
+    <t>sueddeutsche.de/gesundheit</t>
+  </si>
+  <si>
+    <t>faz.net/aktuell/gesellschaft/gesundheit/</t>
+  </si>
+  <si>
+    <t>faz.net/aktuell/politik/inland/</t>
+  </si>
+  <si>
+    <t>sueddeutsche.de/thema/Deutschland</t>
+  </si>
+  <si>
+    <t>spiegel.de/thema/bundesregierung/</t>
+  </si>
+  <si>
+    <t>spiegel.de/thema/bundestag/</t>
+  </si>
+  <si>
+    <t>spiegel.de/gesundheit/</t>
+  </si>
+  <si>
+    <t>faz.net/aktuell/wissen/krebsmedizin/</t>
+  </si>
+  <si>
+    <t>faz.net/aktuell/wissen/leben-gene/</t>
+  </si>
+  <si>
+    <t>spiegel.de/thema/leben/</t>
+  </si>
+  <si>
+    <t>spiegel.de/thema/meinung/</t>
+  </si>
+  <si>
+    <t>spiegel.de/wirtschaft/</t>
+  </si>
+  <si>
+    <t>faz.net/aktuell/wissen/forschung-politik/</t>
+  </si>
+  <si>
+    <t>spiegel.de/netzwelt/web/</t>
+  </si>
+  <si>
+    <t>spiegel.de/netzwelt/netzpolitik/</t>
+  </si>
+  <si>
+    <t>spiegel.de/netzwelt/apps/</t>
+  </si>
+  <si>
+    <t>spiegel.de/psychologie/</t>
+  </si>
+  <si>
+    <t>faz.net/aktuell/wissen/medizin-ernaehrung/</t>
+  </si>
+  <si>
+    <t>faz.net/aktuell/technik-motor/digital/</t>
+  </si>
+  <si>
+    <t>faz.net/aktuell/wirtschaft/</t>
+  </si>
+  <si>
+    <t>sueddeutsche.de/wirtschaft</t>
+  </si>
+  <si>
+    <t>sueddeutsche.de/wissen</t>
+  </si>
+  <si>
+    <t>sueddeutsche.de/thema</t>
+  </si>
+  <si>
+    <t>faz.net/aktuell/wissen/geist-soziales/</t>
+  </si>
+  <si>
+    <t>faz.net/aktuell/feuilleton/debatten/</t>
+  </si>
+  <si>
+    <t>faz.net/aktuell/technik-motor/technik/</t>
+  </si>
+  <si>
+    <t>sueddeutsche.de/meinung</t>
+  </si>
+  <si>
+    <t>sueddeutsche.de/leben</t>
+  </si>
+  <si>
+    <t>sueddeutsche.de/thema/Bundesregierung</t>
+  </si>
+  <si>
+    <t>spiegel.de/wissenschaft/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -86,8 +182,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -368,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -382,18 +479,188 @@
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
